--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_KOSNER BASKONIA VITORIA-GASTEIZ.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_KOSNER BASKONIA VITORIA-GASTEIZ.xlsx
@@ -671,13 +671,13 @@
         <v>0.2797482837528604</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>272</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>302</v>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>251</v>
       </c>
       <c r="M2" t="n">
         <v>318</v>
@@ -752,13 +752,13 @@
         <v>1.046235138705416</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.005847953216374269</v>
+        <v>0.7953216374269005</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.01083032490974729</v>
+        <v>1.090252707581227</v>
       </c>
       <c r="AM2" t="n">
-        <v>2</v>
+        <v>1.651315789473684</v>
       </c>
       <c r="AN2" t="n">
         <v>1.406779661016949</v>
@@ -801,13 +801,13 @@
         <v>0.2797482837528604</v>
       </c>
       <c r="J3" t="n">
-        <v>0.07407407407407407</v>
+        <v>10.07407407407407</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1111111111111111</v>
+        <v>11.18518518518519</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1481481481481481</v>
+        <v>9.296296296296296</v>
       </c>
       <c r="M3" t="n">
         <v>11.77777777777778</v>
@@ -882,13 +882,13 @@
         <v>1.046235138705416</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.005847953216374269</v>
+        <v>0.7953216374269007</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.01083032490974729</v>
+        <v>1.090252707581227</v>
       </c>
       <c r="AM3" t="n">
-        <v>2</v>
+        <v>1.651315789473684</v>
       </c>
       <c r="AN3" t="n">
         <v>1.406779661016949</v>
@@ -931,13 +931,13 @@
         <v>0.2832009080590238</v>
       </c>
       <c r="J4" t="n">
-        <v>12</v>
+        <v>303</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>304</v>
       </c>
       <c r="L4" t="n">
-        <v>16</v>
+        <v>296</v>
       </c>
       <c r="M4" t="n">
         <v>307</v>
@@ -1012,13 +1012,13 @@
         <v>1.234206471494607</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.03389830508474576</v>
+        <v>0.8559322033898306</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.03424657534246575</v>
+        <v>1.041095890410959</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.666666666666667</v>
+        <v>1.566137566137566</v>
       </c>
       <c r="AN4" t="n">
         <v>1.406432748538012</v>
@@ -1061,13 +1061,13 @@
         <v>0.2832009080590238</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4444444444444444</v>
+        <v>11.22222222222222</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3703703703703703</v>
+        <v>11.25925925925926</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5925925925925926</v>
+        <v>10.96296296296296</v>
       </c>
       <c r="M5" t="n">
         <v>11.37037037037037</v>
@@ -1142,13 +1142,13 @@
         <v>1.234206471494607</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.03389830508474576</v>
+        <v>0.8559322033898304</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.03424657534246575</v>
+        <v>1.041095890410959</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.666666666666667</v>
+        <v>1.566137566137566</v>
       </c>
       <c r="AN5" t="n">
         <v>1.406432748538012</v>
@@ -1486,16 +1486,16 @@
         <v>168</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y8" t="n">
         <v>29</v>
@@ -1651,16 +1651,16 @@
         <v>338</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V9" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y9" t="n">
         <v>101</v>
@@ -1816,16 +1816,16 @@
         <v>286</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="Y10" t="n">
         <v>110</v>
@@ -1981,16 +1981,16 @@
         <v>110</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="n">
         <v>31</v>
@@ -2146,16 +2146,16 @@
         <v>22</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="n">
         <v>6</v>
@@ -2311,16 +2311,16 @@
         <v>285</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y13" t="n">
         <v>114</v>
@@ -2476,16 +2476,16 @@
         <v>12</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="n">
         <v>8</v>
@@ -2641,16 +2641,16 @@
         <v>183</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y15" t="n">
         <v>37</v>
@@ -2806,16 +2806,16 @@
         <v>27</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="n">
         <v>4</v>
@@ -2971,16 +2971,16 @@
         <v>435</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="Y17" t="n">
         <v>142</v>
@@ -3136,16 +3136,16 @@
         <v>143</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Y18" t="n">
         <v>34</v>
@@ -3301,16 +3301,16 @@
         <v>334</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Y19" t="n">
         <v>124</v>
@@ -3466,16 +3466,16 @@
         <v>129</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
         <v>32</v>
@@ -3631,16 +3631,16 @@
         <v>127</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
         <v>36</v>
@@ -3796,7 +3796,7 @@
         <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -3961,16 +3961,16 @@
         <v>150</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="n">
         <v>18</v>
@@ -4786,16 +4786,16 @@
         <v>2812</v>
       </c>
       <c r="U28" t="n">
-        <v>2</v>
+        <v>272</v>
       </c>
       <c r="V28" t="n">
-        <v>3</v>
+        <v>302</v>
       </c>
       <c r="W28" t="n">
-        <v>4</v>
+        <v>251</v>
       </c>
       <c r="X28" t="n">
-        <v>2</v>
+        <v>152</v>
       </c>
       <c r="Y28" t="n">
         <v>828</v>
@@ -4951,16 +4951,16 @@
         <v>2964</v>
       </c>
       <c r="U29" t="n">
-        <v>12</v>
+        <v>303</v>
       </c>
       <c r="V29" t="n">
-        <v>10</v>
+        <v>304</v>
       </c>
       <c r="W29" t="n">
-        <v>16</v>
+        <v>296</v>
       </c>
       <c r="X29" t="n">
-        <v>6</v>
+        <v>189</v>
       </c>
       <c r="Y29" t="n">
         <v>850</v>
@@ -5175,16 +5175,16 @@
         <v>168</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.059</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.824</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.706</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>0.824</v>
       </c>
       <c r="Y31" t="n">
         <v>1.706</v>
@@ -5340,16 +5340,16 @@
         <v>338</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="V32" t="n">
-        <v>0.111</v>
+        <v>2.111</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>0.593</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="Y32" t="n">
         <v>3.741</v>
@@ -5505,16 +5505,16 @@
         <v>286</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="W33" t="n">
-        <v>0.08</v>
+        <v>1.08</v>
       </c>
       <c r="X33" t="n">
-        <v>0.04</v>
+        <v>0.68</v>
       </c>
       <c r="Y33" t="n">
         <v>4.4</v>
@@ -5670,16 +5670,16 @@
         <v>110</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>0.474</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>0.579</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>0.316</v>
       </c>
       <c r="Y34" t="n">
         <v>1.632</v>
@@ -5835,16 +5835,16 @@
         <v>22</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>0.261</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.174</v>
       </c>
       <c r="Y35" t="n">
         <v>0.261</v>
@@ -6000,16 +6000,16 @@
         <v>285</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.217</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.696</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>0.826</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.522</v>
       </c>
       <c r="Y36" t="n">
         <v>4.957</v>
@@ -6165,16 +6165,16 @@
         <v>12</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
         <v>4</v>
@@ -6330,16 +6330,16 @@
         <v>183</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Y38" t="n">
         <v>1.85</v>
@@ -6495,16 +6495,16 @@
         <v>27</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
         <v>2</v>
@@ -6660,16 +6660,16 @@
         <v>435</v>
       </c>
       <c r="U40" t="n">
-        <v>0.08</v>
+        <v>2</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W40" t="n">
-        <v>0.08</v>
+        <v>2.16</v>
       </c>
       <c r="X40" t="n">
-        <v>0.04</v>
+        <v>1.32</v>
       </c>
       <c r="Y40" t="n">
         <v>5.68</v>
@@ -6825,16 +6825,16 @@
         <v>143</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>0.385</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>0.346</v>
       </c>
       <c r="Y41" t="n">
         <v>1.308</v>
@@ -6990,16 +6990,16 @@
         <v>334</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y42" t="n">
         <v>4.96</v>
@@ -7155,16 +7155,16 @@
         <v>129</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="Y43" t="n">
         <v>1.28</v>
@@ -7320,16 +7320,16 @@
         <v>127</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>0.588</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>0.176</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>0.176</v>
       </c>
       <c r="Y44" t="n">
         <v>2.118</v>
@@ -7485,7 +7485,7 @@
         <v>2</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -7650,16 +7650,16 @@
         <v>150</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>0.889</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="Y46" t="n">
         <v>0.667</v>
@@ -8475,16 +8475,16 @@
         <v>2812</v>
       </c>
       <c r="U51" t="n">
-        <v>0.074</v>
+        <v>10.074</v>
       </c>
       <c r="V51" t="n">
-        <v>0.111</v>
+        <v>11.185</v>
       </c>
       <c r="W51" t="n">
-        <v>0.148</v>
+        <v>9.295999999999999</v>
       </c>
       <c r="X51" t="n">
-        <v>0.074</v>
+        <v>5.63</v>
       </c>
       <c r="Y51" t="n">
         <v>30.667</v>
@@ -8640,16 +8640,16 @@
         <v>2964</v>
       </c>
       <c r="U52" t="n">
-        <v>0.444</v>
+        <v>11.222</v>
       </c>
       <c r="V52" t="n">
-        <v>0.37</v>
+        <v>11.259</v>
       </c>
       <c r="W52" t="n">
-        <v>0.593</v>
+        <v>10.963</v>
       </c>
       <c r="X52" t="n">
-        <v>0.222</v>
+        <v>7</v>
       </c>
       <c r="Y52" t="n">
         <v>31.481</v>
